--- a/SIO2-B1 - 2.3 - Tableau de synthèse - Épreuve E5 - BTS SIO 2025.xlsx
+++ b/SIO2-B1 - 2.3 - Tableau de synthèse - Épreuve E5 - BTS SIO 2025.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29926"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cours\SIO2\B1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yassy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{EC00A524-0E5B-496A-8D96-3E99C7FD5107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AF30D70-4A53-4C10-904D-E9F9499119B0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C20681-54D6-44F2-90C1-B1A7EFF370C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$45</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -30,16 +30,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -53,16 +54,10 @@
     <t xml:space="preserve">NOM et prénom : AKHOURFI Yassine </t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Centre de formation : Carriat</t>
   </si>
   <si>
     <t>Option :</t>
-  </si>
-  <si>
-    <t>▢ SISR</t>
   </si>
   <si>
     <t>▢ SLAM</t>
@@ -136,6 +131,74 @@
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
+  </si>
+  <si>
+    <t>TP Haute disponibilté</t>
+  </si>
+  <si>
+    <t>Projet AP</t>
+  </si>
+  <si>
+    <t>Tp PowerShell</t>
+  </si>
+  <si>
+    <t>Tp AD GPO (Administration système)</t>
+  </si>
+  <si>
+    <t>Tp syslog</t>
+  </si>
+  <si>
+    <t>Tp WDS MDT</t>
+  </si>
+  <si>
+    <t>Tp AD DNS DHCP</t>
+  </si>
+  <si>
+    <t>TP Maintenance et sécurisation du matériel réseaux</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="22"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SISR</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Gestion de données </t>
+  </si>
+  <si>
+    <t>26/05/25 au 4/07/25</t>
+  </si>
+  <si>
+    <t>19/01/26 au 27/02/26</t>
+  </si>
+  <si>
+    <t>Préparation et configuration de postes informatiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     X</t>
+  </si>
+  <si>
+    <t>N° candidat : 02249648189</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://yugi-droid.github.io/portfolio-akhourfi/?classId</t>
   </si>
 </sst>
 </file>
@@ -145,7 +208,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -207,6 +270,39 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="28"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -216,7 +312,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -476,12 +572,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="2" tint="-0.749992370372631"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.749992370372631"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -546,6 +697,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -573,6 +752,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -587,6 +775,21 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -896,171 +1099,135 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ82"/>
-  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="12.75"/>
+  <dimension ref="A1:AQ91"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
     <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
     <col min="9" max="43" width="11.42578125" customWidth="1"/>
     <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="22"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1">
-      <c r="A2" s="22" t="s">
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1">
-      <c r="A3" s="23" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="24"/>
-      <c r="H3" s="25"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="33" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="34"/>
+      <c r="H3" s="35"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A4" s="23" t="s">
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="13" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="B6" s="47" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:43" ht="90" customHeight="1">
-      <c r="A5" s="26" t="s">
+      <c r="C6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="D6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="H6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="6" t="s">
+    </row>
+    <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="37"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="D7" s="20" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="6" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1">
-      <c r="A6" s="27"/>
-      <c r="B6" s="35"/>
-      <c r="C6" s="20" t="s">
+      <c r="E7" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="F7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="G7" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="H7" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6"/>
-      <c r="J6"/>
-      <c r="K6"/>
-      <c r="L6"/>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6"/>
-      <c r="R6"/>
-      <c r="S6"/>
-      <c r="T6"/>
-      <c r="U6"/>
-      <c r="V6"/>
-      <c r="W6"/>
-      <c r="X6"/>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6"/>
-      <c r="AB6"/>
-      <c r="AC6"/>
-      <c r="AD6"/>
-      <c r="AE6"/>
-      <c r="AF6"/>
-      <c r="AG6"/>
-      <c r="AH6"/>
-      <c r="AI6"/>
-      <c r="AJ6"/>
-      <c r="AK6"/>
-      <c r="AL6"/>
-      <c r="AM6"/>
-      <c r="AN6"/>
-      <c r="AO6"/>
-      <c r="AP6"/>
-      <c r="AQ6"/>
-    </row>
-    <row r="7" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="30"/>
       <c r="I7"/>
       <c r="J7"/>
       <c r="K7"/>
@@ -1097,15 +1264,17 @@
       <c r="AP7"/>
       <c r="AQ7"/>
     </row>
-    <row r="8" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A8" s="9"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17"/>
+    <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1142,10 +1311,10 @@
       <c r="AP8"/>
       <c r="AQ8"/>
     </row>
-    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="9" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="9"/>
       <c r="B9" s="8"/>
-      <c r="C9" s="16"/>
+      <c r="C9" s="15"/>
       <c r="D9" s="16"/>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
@@ -1187,7 +1356,7 @@
       <c r="AP9"/>
       <c r="AQ9"/>
     </row>
-    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="10" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9"/>
       <c r="B10" s="8"/>
       <c r="C10" s="16"/>
@@ -1232,7 +1401,7 @@
       <c r="AP10"/>
       <c r="AQ10"/>
     </row>
-    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="11" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9"/>
       <c r="B11" s="8"/>
       <c r="C11" s="16"/>
@@ -1277,7 +1446,7 @@
       <c r="AP11"/>
       <c r="AQ11"/>
     </row>
-    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="12" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9"/>
       <c r="B12" s="8"/>
       <c r="C12" s="16"/>
@@ -1322,7 +1491,7 @@
       <c r="AP12"/>
       <c r="AQ12"/>
     </row>
-    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="13" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9"/>
       <c r="B13" s="8"/>
       <c r="C13" s="16"/>
@@ -1367,7 +1536,7 @@
       <c r="AP13"/>
       <c r="AQ13"/>
     </row>
-    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="14" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="9"/>
       <c r="B14" s="8"/>
       <c r="C14" s="16"/>
@@ -1412,7 +1581,7 @@
       <c r="AP14"/>
       <c r="AQ14"/>
     </row>
-    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="15" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="9"/>
       <c r="B15" s="8"/>
       <c r="C15" s="16"/>
@@ -1457,7 +1626,7 @@
       <c r="AP15"/>
       <c r="AQ15"/>
     </row>
-    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="16" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="9"/>
       <c r="B16" s="8"/>
       <c r="C16" s="16"/>
@@ -1502,7 +1671,7 @@
       <c r="AP16"/>
       <c r="AQ16"/>
     </row>
-    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
+    <row r="17" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="9"/>
       <c r="B17" s="8"/>
       <c r="C17" s="16"/>
@@ -1547,17 +1716,23 @@
       <c r="AP17"/>
       <c r="AQ17"/>
     </row>
-    <row r="18" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A18" s="31" t="s">
+    <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H18" s="25"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1594,15 +1769,25 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A19" s="9"/>
+    <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>25</v>
+      </c>
       <c r="B19" s="8"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17"/>
+      <c r="C19" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>32</v>
+      </c>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1639,15 +1824,23 @@
       <c r="AP19"/>
       <c r="AQ19"/>
     </row>
-    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A20" s="9"/>
+    <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="22" t="s">
+        <v>26</v>
+      </c>
       <c r="B20" s="8"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="17"/>
+      <c r="C20" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H20" s="27"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1684,15 +1877,23 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A21" s="9"/>
+    <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="22" t="s">
+        <v>27</v>
+      </c>
       <c r="B21" s="8"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="17"/>
+      <c r="C21" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H21" s="27"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1729,15 +1930,23 @@
       <c r="AP21"/>
       <c r="AQ21"/>
     </row>
-    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A22" s="9"/>
+    <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="22" t="s">
+        <v>28</v>
+      </c>
       <c r="B22" s="8"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="17"/>
+      <c r="C22" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="27"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1774,15 +1983,23 @@
       <c r="AP22"/>
       <c r="AQ22"/>
     </row>
-    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A23" s="9"/>
+    <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="B23" s="8"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="17"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="27" t="s">
+        <v>32</v>
+      </c>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -1819,15 +2036,21 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A24" s="9"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="B24" s="8"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="17"/>
+      <c r="C24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="27"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -1864,15 +2087,21 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A25" s="9"/>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="22" t="s">
+        <v>31</v>
+      </c>
       <c r="B25" s="8"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="17"/>
+      <c r="C25" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="27"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -1909,15 +2138,17 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="17"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A26" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="43"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -1954,17 +2185,15 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="2" customFormat="1" ht="18">
-      <c r="A27" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
+    <row r="27" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="17"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2001,7 +2230,7 @@
       <c r="AP27"/>
       <c r="AQ27"/>
     </row>
-    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="28" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9"/>
       <c r="B28" s="8"/>
       <c r="C28" s="16"/>
@@ -2046,7 +2275,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="29" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9"/>
       <c r="B29" s="8"/>
       <c r="C29" s="16"/>
@@ -2091,7 +2320,7 @@
       <c r="AP29"/>
       <c r="AQ29"/>
     </row>
-    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="30" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="9"/>
       <c r="B30" s="8"/>
       <c r="C30" s="16"/>
@@ -2136,7 +2365,7 @@
       <c r="AP30"/>
       <c r="AQ30"/>
     </row>
-    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="31" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="9"/>
       <c r="B31" s="8"/>
       <c r="C31" s="16"/>
@@ -2181,7 +2410,7 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="16"/>
@@ -2226,7 +2455,7 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="9"/>
       <c r="B33" s="8"/>
       <c r="C33" s="16"/>
@@ -2271,14 +2500,20 @@
       <c r="AP33"/>
       <c r="AQ33"/>
     </row>
-    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1">
-      <c r="A34" s="9"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+    <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
       <c r="H34" s="17"/>
       <c r="I34"/>
       <c r="J34"/>
@@ -2316,15 +2551,23 @@
       <c r="AP34"/>
       <c r="AQ34"/>
     </row>
-    <row r="35" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-      <c r="H35" s="19"/>
+    <row r="35" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" s="17"/>
       <c r="I35"/>
       <c r="J35"/>
       <c r="K35"/>
@@ -2361,15 +2604,17 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" s="2" customFormat="1" ht="15">
-      <c r="A36" s="5"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+    <row r="36" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A36" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="45"/>
+      <c r="C36" s="45"/>
+      <c r="D36" s="45"/>
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="46"/>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
@@ -2406,60 +2651,473 @@
       <c r="AP36"/>
       <c r="AQ36"/>
     </row>
-    <row r="37" spans="1:43" customFormat="1"/>
-    <row r="38" spans="1:43" customFormat="1"/>
-    <row r="39" spans="1:43" customFormat="1"/>
-    <row r="40" spans="1:43" customFormat="1"/>
-    <row r="41" spans="1:43" customFormat="1"/>
-    <row r="42" spans="1:43" customFormat="1"/>
-    <row r="43" spans="1:43" customFormat="1"/>
-    <row r="44" spans="1:43" customFormat="1"/>
-    <row r="45" spans="1:43" customFormat="1"/>
-    <row r="46" spans="1:43" customFormat="1"/>
-    <row r="47" spans="1:43" customFormat="1"/>
-    <row r="48" spans="1:43" customFormat="1"/>
-    <row r="49" customFormat="1"/>
-    <row r="50" customFormat="1"/>
-    <row r="51" customFormat="1"/>
-    <row r="52" customFormat="1"/>
-    <row r="53" customFormat="1"/>
-    <row r="54" customFormat="1"/>
-    <row r="55" customFormat="1"/>
-    <row r="56" customFormat="1"/>
-    <row r="57" customFormat="1"/>
-    <row r="58" customFormat="1"/>
-    <row r="59" customFormat="1"/>
-    <row r="60" customFormat="1"/>
-    <row r="61" customFormat="1"/>
-    <row r="62" customFormat="1"/>
-    <row r="63" customFormat="1"/>
-    <row r="64" customFormat="1"/>
-    <row r="65" customFormat="1"/>
-    <row r="66" customFormat="1"/>
-    <row r="67" customFormat="1"/>
-    <row r="68" customFormat="1"/>
-    <row r="69" customFormat="1"/>
-    <row r="70" customFormat="1"/>
-    <row r="71" customFormat="1"/>
-    <row r="72" customFormat="1"/>
-    <row r="73" customFormat="1"/>
-    <row r="74" customFormat="1"/>
-    <row r="75" customFormat="1"/>
-    <row r="76" customFormat="1"/>
-    <row r="77" customFormat="1"/>
-    <row r="78" customFormat="1"/>
-    <row r="79" customFormat="1"/>
-    <row r="80" customFormat="1"/>
-    <row r="81" customFormat="1"/>
-    <row r="82" customFormat="1"/>
+    <row r="37" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="9"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="17"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
+      <c r="AF37"/>
+      <c r="AG37"/>
+      <c r="AH37"/>
+      <c r="AI37"/>
+      <c r="AJ37"/>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
+      <c r="AN37"/>
+      <c r="AO37"/>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+    </row>
+    <row r="38" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="17"/>
+      <c r="I38"/>
+      <c r="J38"/>
+      <c r="K38"/>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+      <c r="R38"/>
+      <c r="S38"/>
+      <c r="T38"/>
+      <c r="U38"/>
+      <c r="V38"/>
+      <c r="W38"/>
+      <c r="X38"/>
+      <c r="Y38"/>
+      <c r="Z38"/>
+      <c r="AA38"/>
+      <c r="AB38"/>
+      <c r="AC38"/>
+      <c r="AD38"/>
+      <c r="AE38"/>
+      <c r="AF38"/>
+      <c r="AG38"/>
+      <c r="AH38"/>
+      <c r="AI38"/>
+      <c r="AJ38"/>
+      <c r="AK38"/>
+      <c r="AL38"/>
+      <c r="AM38"/>
+      <c r="AN38"/>
+      <c r="AO38"/>
+      <c r="AP38"/>
+      <c r="AQ38"/>
+    </row>
+    <row r="39" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+      <c r="G39" s="16"/>
+      <c r="H39" s="17"/>
+      <c r="I39"/>
+      <c r="J39"/>
+      <c r="K39"/>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+      <c r="R39"/>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
+      <c r="V39"/>
+      <c r="W39"/>
+      <c r="X39"/>
+      <c r="Y39"/>
+      <c r="Z39"/>
+      <c r="AA39"/>
+      <c r="AB39"/>
+      <c r="AC39"/>
+      <c r="AD39"/>
+      <c r="AE39"/>
+      <c r="AF39"/>
+      <c r="AG39"/>
+      <c r="AH39"/>
+      <c r="AI39"/>
+      <c r="AJ39"/>
+      <c r="AK39"/>
+      <c r="AL39"/>
+      <c r="AM39"/>
+      <c r="AN39"/>
+      <c r="AO39"/>
+      <c r="AP39"/>
+      <c r="AQ39"/>
+    </row>
+    <row r="40" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
+      <c r="H40" s="17"/>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+      <c r="R40"/>
+      <c r="S40"/>
+      <c r="T40"/>
+      <c r="U40"/>
+      <c r="V40"/>
+      <c r="W40"/>
+      <c r="X40"/>
+      <c r="Y40"/>
+      <c r="Z40"/>
+      <c r="AA40"/>
+      <c r="AB40"/>
+      <c r="AC40"/>
+      <c r="AD40"/>
+      <c r="AE40"/>
+      <c r="AF40"/>
+      <c r="AG40"/>
+      <c r="AH40"/>
+      <c r="AI40"/>
+      <c r="AJ40"/>
+      <c r="AK40"/>
+      <c r="AL40"/>
+      <c r="AM40"/>
+      <c r="AN40"/>
+      <c r="AO40"/>
+      <c r="AP40"/>
+      <c r="AQ40"/>
+    </row>
+    <row r="41" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+      <c r="H41" s="17"/>
+      <c r="I41"/>
+      <c r="J41"/>
+      <c r="K41"/>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+      <c r="R41"/>
+      <c r="S41"/>
+      <c r="T41"/>
+      <c r="U41"/>
+      <c r="V41"/>
+      <c r="W41"/>
+      <c r="X41"/>
+      <c r="Y41"/>
+      <c r="Z41"/>
+      <c r="AA41"/>
+      <c r="AB41"/>
+      <c r="AC41"/>
+      <c r="AD41"/>
+      <c r="AE41"/>
+      <c r="AF41"/>
+      <c r="AG41"/>
+      <c r="AH41"/>
+      <c r="AI41"/>
+      <c r="AJ41"/>
+      <c r="AK41"/>
+      <c r="AL41"/>
+      <c r="AM41"/>
+      <c r="AN41"/>
+      <c r="AO41"/>
+      <c r="AP41"/>
+      <c r="AQ41"/>
+    </row>
+    <row r="42" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="16"/>
+      <c r="H42" s="17"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+      <c r="R42"/>
+      <c r="S42"/>
+      <c r="T42"/>
+      <c r="U42"/>
+      <c r="V42"/>
+      <c r="W42"/>
+      <c r="X42"/>
+      <c r="Y42"/>
+      <c r="Z42"/>
+      <c r="AA42"/>
+      <c r="AB42"/>
+      <c r="AC42"/>
+      <c r="AD42"/>
+      <c r="AE42"/>
+      <c r="AF42"/>
+      <c r="AG42"/>
+      <c r="AH42"/>
+      <c r="AI42"/>
+      <c r="AJ42"/>
+      <c r="AK42"/>
+      <c r="AL42"/>
+      <c r="AM42"/>
+      <c r="AN42"/>
+      <c r="AO42"/>
+      <c r="AP42"/>
+      <c r="AQ42"/>
+    </row>
+    <row r="43" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="9"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
+      <c r="H43" s="17"/>
+      <c r="I43"/>
+      <c r="J43"/>
+      <c r="K43"/>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+      <c r="R43"/>
+      <c r="S43"/>
+      <c r="T43"/>
+      <c r="U43"/>
+      <c r="V43"/>
+      <c r="W43"/>
+      <c r="X43"/>
+      <c r="Y43"/>
+      <c r="Z43"/>
+      <c r="AA43"/>
+      <c r="AB43"/>
+      <c r="AC43"/>
+      <c r="AD43"/>
+      <c r="AE43"/>
+      <c r="AF43"/>
+      <c r="AG43"/>
+      <c r="AH43"/>
+      <c r="AI43"/>
+      <c r="AJ43"/>
+      <c r="AK43"/>
+      <c r="AL43"/>
+      <c r="AM43"/>
+      <c r="AN43"/>
+      <c r="AO43"/>
+      <c r="AP43"/>
+      <c r="AQ43"/>
+    </row>
+    <row r="44" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C44" s="18"/>
+      <c r="D44" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44"/>
+      <c r="J44"/>
+      <c r="K44"/>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+      <c r="R44"/>
+      <c r="S44"/>
+      <c r="T44"/>
+      <c r="U44"/>
+      <c r="V44"/>
+      <c r="W44"/>
+      <c r="X44"/>
+      <c r="Y44"/>
+      <c r="Z44"/>
+      <c r="AA44"/>
+      <c r="AB44"/>
+      <c r="AC44"/>
+      <c r="AD44"/>
+      <c r="AE44"/>
+      <c r="AF44"/>
+      <c r="AG44"/>
+      <c r="AH44"/>
+      <c r="AI44"/>
+      <c r="AJ44"/>
+      <c r="AK44"/>
+      <c r="AL44"/>
+      <c r="AM44"/>
+      <c r="AN44"/>
+      <c r="AO44"/>
+      <c r="AP44"/>
+      <c r="AQ44"/>
+    </row>
+    <row r="45" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="5"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45"/>
+      <c r="J45"/>
+      <c r="K45"/>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+      <c r="R45"/>
+      <c r="S45"/>
+      <c r="T45"/>
+      <c r="U45"/>
+      <c r="V45"/>
+      <c r="W45"/>
+      <c r="X45"/>
+      <c r="Y45"/>
+      <c r="Z45"/>
+      <c r="AA45"/>
+      <c r="AB45"/>
+      <c r="AC45"/>
+      <c r="AD45"/>
+      <c r="AE45"/>
+      <c r="AF45"/>
+      <c r="AG45"/>
+      <c r="AH45"/>
+      <c r="AI45"/>
+      <c r="AJ45"/>
+      <c r="AK45"/>
+      <c r="AL45"/>
+      <c r="AM45"/>
+      <c r="AN45"/>
+      <c r="AO45"/>
+      <c r="AP45"/>
+      <c r="AQ45"/>
+    </row>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="82" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="83" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="85" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="86" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="88" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="89" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="90" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="B6:B7"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
@@ -2469,7 +3127,7 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="45" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="45" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -2636,13 +3294,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEF2F565-D16B-4E1F-8C14-1502C91A5A59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEF2F565-D16B-4E1F-8C14-1502C91A5A59}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66B9A351-058C-48CB-820F-C4E7B408AE8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66B9A351-058C-48CB-820F-C4E7B408AE8D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2c5b469e-a7d6-41eb-8954-9d04fdb6bfc6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8F0798-7F27-4A8A-AE93-3543E01FAAAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E8F0798-7F27-4A8A-AE93-3543E01FAAAD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="2c5b469e-a7d6-41eb-8954-9d04fdb6bfc6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/SIO2-B1 - 2.3 - Tableau de synthèse - Épreuve E5 - BTS SIO 2025.xlsx
+++ b/SIO2-B1 - 2.3 - Tableau de synthèse - Épreuve E5 - BTS SIO 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yassy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C20681-54D6-44F2-90C1-B1A7EFF370C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D331F5-EEDD-4232-A264-545CD32CEE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$46</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="45">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -123,10 +123,6 @@
 ▸Développer son projet professionnel</t>
   </si>
   <si>
-    <t xml:space="preserve">Réalisation en cours de formation
-</t>
-  </si>
-  <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
@@ -139,22 +135,13 @@
     <t>Projet AP</t>
   </si>
   <si>
-    <t>Tp PowerShell</t>
-  </si>
-  <si>
     <t>Tp AD GPO (Administration système)</t>
   </si>
   <si>
     <t>Tp syslog</t>
   </si>
   <si>
-    <t>Tp WDS MDT</t>
-  </si>
-  <si>
     <t>Tp AD DNS DHCP</t>
-  </si>
-  <si>
-    <t>TP Maintenance et sécurisation du matériel réseaux</t>
   </si>
   <si>
     <t>X</t>
@@ -200,6 +187,31 @@
   <si>
     <t>Adresse URL du portfolio : https://yugi-droid.github.io/portfolio-akhourfi/?classId</t>
   </si>
+  <si>
+    <t>Tp WDS MDT WSUS</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>Gestion des imprimantes</t>
+  </si>
+  <si>
+    <t>Gestion des tickets sur GLPI</t>
+  </si>
+  <si>
+    <t>Modification de profils utilisateurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réalisation en cours de formation
+ </t>
+  </si>
+  <si>
+    <t>https://yugi-droid.github.io/portfolio-akhourfi/#projets</t>
+  </si>
+  <si>
+    <t>https://yugi-droid.github.io/portfolio-akhourfi/#stages</t>
+  </si>
 </sst>
 </file>
 
@@ -208,7 +220,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -303,6 +315,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -628,11 +646,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -725,9 +744,63 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -737,63 +810,14 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Euro" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Lien hypertexte" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1099,7 +1123,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ91"/>
+  <dimension ref="A1:AQ92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
@@ -1110,82 +1134,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="35"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
       <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H4" s="14" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="49"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
+      <c r="A5" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="49" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1208,8 +1232,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="324.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="48"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="20" t="s">
         <v>15</v>
       </c>
@@ -1265,16 +1289,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
+      <c r="A8" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1718,19 +1742,21 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="8"/>
+        <v>23</v>
+      </c>
+      <c r="B18" s="54">
+        <v>46010</v>
+      </c>
       <c r="C18" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E18" s="24"/>
       <c r="F18" s="24"/>
       <c r="G18" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H18" s="25"/>
       <c r="I18"/>
@@ -1771,22 +1797,24 @@
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="8"/>
+        <v>24</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>38</v>
+      </c>
       <c r="C19" s="26" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H19" s="27" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I19"/>
       <c r="J19"/>
@@ -1826,22 +1854,26 @@
     </row>
     <row r="20" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="8"/>
+        <v>25</v>
+      </c>
+      <c r="B20" s="54">
+        <v>45917</v>
+      </c>
       <c r="C20" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="23"/>
       <c r="G20" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H20" s="27"/>
-      <c r="I20"/>
+      <c r="I20" s="55" t="s">
+        <v>43</v>
+      </c>
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20"/>
@@ -1879,19 +1911,21 @@
     </row>
     <row r="21" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="8"/>
+        <v>26</v>
+      </c>
+      <c r="B21" s="54">
+        <v>46106</v>
+      </c>
       <c r="C21" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E21" s="23"/>
       <c r="F21" s="23"/>
       <c r="G21" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H21" s="27"/>
       <c r="I21"/>
@@ -1932,21 +1966,23 @@
     </row>
     <row r="22" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="54">
+        <v>45910</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23" t="s">
         <v>28</v>
-      </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>32</v>
       </c>
       <c r="E22" s="23"/>
       <c r="F22" s="23"/>
       <c r="G22" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="27"/>
+        <v>28</v>
+      </c>
+      <c r="H22" s="27" t="s">
+        <v>28</v>
+      </c>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1984,22 +2020,22 @@
       <c r="AQ22"/>
     </row>
     <row r="23" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23" s="54">
+        <v>45917</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>28</v>
+      </c>
       <c r="D23" s="23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E23" s="23"/>
       <c r="F23" s="23"/>
-      <c r="G23" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="27" t="s">
-        <v>32</v>
-      </c>
+      <c r="G23" s="23"/>
+      <c r="H23" s="27"/>
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23"/>
@@ -2036,21 +2072,17 @@
       <c r="AP23"/>
       <c r="AQ23"/>
     </row>
-    <row r="24" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="27"/>
+    <row r="24" spans="1:43" s="2" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="45"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2087,21 +2119,15 @@
       <c r="AP24"/>
       <c r="AQ24"/>
     </row>
-    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
-        <v>31</v>
-      </c>
+    <row r="25" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="9"/>
       <c r="B25" s="8"/>
-      <c r="C25" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="27"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="17"/>
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25"/>
@@ -2138,17 +2164,15 @@
       <c r="AP25"/>
       <c r="AQ25"/>
     </row>
-    <row r="26" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A26" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
+    <row r="26" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="9"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="17"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2410,14 +2434,20 @@
       <c r="AP31"/>
       <c r="AQ31"/>
     </row>
-    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="16"/>
+    <row r="32" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
       <c r="H32" s="17"/>
       <c r="I32"/>
       <c r="J32"/>
@@ -2455,14 +2485,22 @@
       <c r="AP32"/>
       <c r="AQ32"/>
     </row>
-    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
+    <row r="33" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="29"/>
+      <c r="D33" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="30" t="s">
+        <v>28</v>
+      </c>
       <c r="H33" s="17"/>
       <c r="I33"/>
       <c r="J33"/>
@@ -2502,20 +2540,24 @@
     </row>
     <row r="34" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A34" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D34" s="29"/>
+        <v>39</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="29"/>
+      <c r="D34" s="30" t="s">
+        <v>28</v>
+      </c>
       <c r="E34" s="29"/>
       <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
+      <c r="G34" s="30" t="s">
+        <v>28</v>
+      </c>
       <c r="H34" s="17"/>
-      <c r="I34"/>
+      <c r="I34" s="55" t="s">
+        <v>44</v>
+      </c>
       <c r="J34"/>
       <c r="K34"/>
       <c r="L34"/>
@@ -2553,20 +2595,18 @@
     </row>
     <row r="35" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A35" s="9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C35" s="29"/>
       <c r="D35" s="30" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E35" s="29"/>
       <c r="F35" s="29"/>
-      <c r="G35" s="30" t="s">
-        <v>32</v>
-      </c>
+      <c r="G35" s="30"/>
       <c r="H35" s="17"/>
       <c r="I35"/>
       <c r="J35"/>
@@ -2604,17 +2644,23 @@
       <c r="AP35"/>
       <c r="AQ35"/>
     </row>
-    <row r="36" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A36" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="B36" s="45"/>
-      <c r="C36" s="45"/>
-      <c r="D36" s="45"/>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="46"/>
+    <row r="36" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A36" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="30"/>
+      <c r="H36" s="17"/>
       <c r="I36"/>
       <c r="J36"/>
       <c r="K36"/>
@@ -2651,15 +2697,17 @@
       <c r="AP36"/>
       <c r="AQ36"/>
     </row>
-    <row r="37" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="17"/>
+    <row r="37" spans="1:43" s="2" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A37" s="46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B37" s="47"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
+      <c r="G37" s="47"/>
+      <c r="H37" s="48"/>
       <c r="I37"/>
       <c r="J37"/>
       <c r="K37"/>
@@ -2966,23 +3014,15 @@
       <c r="AP43"/>
       <c r="AQ43"/>
     </row>
-    <row r="44" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="H44" s="19"/>
+    <row r="44" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="9"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
+      <c r="G44" s="16"/>
+      <c r="H44" s="17"/>
       <c r="I44"/>
       <c r="J44"/>
       <c r="K44"/>
@@ -3019,16 +3059,26 @@
       <c r="AP44"/>
       <c r="AQ44"/>
     </row>
-    <row r="45" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="5"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45"/>
+    <row r="45" spans="1:43" s="2" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="18"/>
+      <c r="D45" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="55" t="s">
+        <v>44</v>
+      </c>
       <c r="J45"/>
       <c r="K45"/>
       <c r="L45"/>
@@ -3064,7 +3114,51 @@
       <c r="AP45"/>
       <c r="AQ45"/>
     </row>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:43" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="5"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46"/>
+      <c r="J46"/>
+      <c r="K46"/>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+      <c r="R46"/>
+      <c r="S46"/>
+      <c r="T46"/>
+      <c r="U46"/>
+      <c r="V46"/>
+      <c r="W46"/>
+      <c r="X46"/>
+      <c r="Y46"/>
+      <c r="Z46"/>
+      <c r="AA46"/>
+      <c r="AB46"/>
+      <c r="AC46"/>
+      <c r="AD46"/>
+      <c r="AE46"/>
+      <c r="AF46"/>
+      <c r="AG46"/>
+      <c r="AH46"/>
+      <c r="AI46"/>
+      <c r="AJ46"/>
+      <c r="AK46"/>
+      <c r="AL46"/>
+      <c r="AM46"/>
+      <c r="AN46"/>
+      <c r="AO46"/>
+      <c r="AP46"/>
+      <c r="AQ46"/>
+    </row>
     <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -3110,43 +3204,49 @@
     <row r="89" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="90" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="91" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="92" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="B6:B7"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="I34" r:id="rId1" location="stages" xr:uid="{6806E1BB-7165-4862-AC33-310EECB3365B}"/>
+    <hyperlink ref="I45" r:id="rId2" location="stages" xr:uid="{5589A0CE-8BC5-4FBD-BEDD-02FCB921C935}"/>
+    <hyperlink ref="I20" r:id="rId3" location="projets" xr:uid="{2ECFFFD1-9C4A-4DF7-9A8D-4ACC335A64EA}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="45" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" orientation="portrait" r:id="rId4"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Aquis xmlns="2c5b469e-a7d6-41eb-8954-9d04fdb6bfc6">true</Aquis>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Aquis xmlns="2c5b469e-a7d6-41eb-8954-9d04fdb6bfc6">true</Aquis>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3294,19 +3394,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEF2F565-D16B-4E1F-8C14-1502C91A5A59}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66B9A351-058C-48CB-820F-C4E7B408AE8D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="2c5b469e-a7d6-41eb-8954-9d04fdb6bfc6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66B9A351-058C-48CB-820F-C4E7B408AE8D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AEF2F565-D16B-4E1F-8C14-1502C91A5A59}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="2c5b469e-a7d6-41eb-8954-9d04fdb6bfc6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
